--- a/artfynd/A 36924-2024 artfynd.xlsx
+++ b/artfynd/A 36924-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>75642517</v>
       </c>
       <c r="B2" t="n">
-        <v>78458</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>462150.7444476392</v>
+        <v>462151</v>
       </c>
       <c r="R2" t="n">
-        <v>6886202.781546409</v>
+        <v>6886203</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -748,19 +743,9 @@
           <t>2018-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101998504</v>
+        <v>101998459</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>462084.1859276786</v>
+        <v>462040</v>
       </c>
       <c r="R3" t="n">
-        <v>6886247.071346156</v>
+        <v>6886322</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,19 +863,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101998459</v>
+        <v>101998504</v>
       </c>
       <c r="B4" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -975,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462040.0167287402</v>
+        <v>462084</v>
       </c>
       <c r="R4" t="n">
-        <v>6886322.480735824</v>
+        <v>6886247</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,19 +973,9 @@
           <t>2022-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 36924-2024 artfynd.xlsx
+++ b/artfynd/A 36924-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75642517</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101998459</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,8 +1015,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101998504</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>